--- a/Deliverables/BOM/JLCPCB_BOM.xlsx
+++ b/Deliverables/BOM/JLCPCB_BOM.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ezlo-irblaster\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\ezlo-irblaster\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C7228B-5647-479F-9F07-D6936B6FEE4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="99">
   <si>
     <t>Comment</t>
   </si>
@@ -70,9 +69,6 @@
     <t>IR333-A</t>
   </si>
   <si>
-    <t>TEST POINT</t>
-  </si>
-  <si>
     <t>YJL2302B</t>
   </si>
   <si>
@@ -103,9 +99,6 @@
     <t>IRM-H638T/TR2</t>
   </si>
   <si>
-    <t>IRM-3638T</t>
-  </si>
-  <si>
     <t>LR1107G-33-AB3-C-R</t>
   </si>
   <si>
@@ -157,9 +150,6 @@
     <t>LED3, LED4, LED5, LED6, LED7, LED8, LED9, LED10</t>
   </si>
   <si>
-    <t>P2, P3, P4</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
@@ -190,9 +180,6 @@
     <t>U2</t>
   </si>
   <si>
-    <t>U3</t>
-  </si>
-  <si>
     <t>U4</t>
   </si>
   <si>
@@ -229,9 +216,6 @@
     <t>IR333_A</t>
   </si>
   <si>
-    <t>Test-point</t>
-  </si>
-  <si>
     <t>SOT-23-3L_</t>
   </si>
   <si>
@@ -253,9 +237,6 @@
     <t>SMD-4,4x5mm</t>
   </si>
   <si>
-    <t>SIP-3P-2.54mm</t>
-  </si>
-  <si>
     <t>SOT-89-3</t>
   </si>
   <si>
@@ -265,9 +246,6 @@
     <t>C602037</t>
   </si>
   <si>
-    <t>C2181865</t>
-  </si>
-  <si>
     <t>C14664</t>
   </si>
   <si>
@@ -277,9 +255,6 @@
     <t>C69335</t>
   </si>
   <si>
-    <t>C2168289</t>
-  </si>
-  <si>
     <t>C107198</t>
   </si>
   <si>
@@ -301,15 +276,9 @@
     <t>C699316</t>
   </si>
   <si>
-    <t>C2092011</t>
-  </si>
-  <si>
     <t>C105879</t>
   </si>
   <si>
-    <t>C2960734</t>
-  </si>
-  <si>
     <t>C105588</t>
   </si>
   <si>
@@ -325,20 +294,35 @@
     <t>C91447</t>
   </si>
   <si>
-    <t>C16216</t>
-  </si>
-  <si>
     <t>C171498</t>
   </si>
   <si>
-    <t>-</t>
+    <t>C90692</t>
+  </si>
+  <si>
+    <t>C23186</t>
+  </si>
+  <si>
+    <t>C145963</t>
+  </si>
+  <si>
+    <t>C346144</t>
+  </si>
+  <si>
+    <t>C307331</t>
+  </si>
+  <si>
+    <t>C96446</t>
+  </si>
+  <si>
+    <t>C25804</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,48 +330,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -395,139 +347,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -813,419 +638,392 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" s="2" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="4" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="2" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="4" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="2" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="4" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="2" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="2" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="4" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="2" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="2" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="2" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>